--- a/docs/AI_logs/NguyenVanAn_AI_AuditLog.xlsx
+++ b/docs/AI_logs/NguyenVanAn_AI_AuditLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\PROJECT\github project\csd201\Call_Center_Waiting_Line_System\docs\AI_logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09C16FB5-1D98-4CD4-B909-2C30EC4D8BE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E38610E-F38E-466A-9D17-12F755661BEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2031,7 +2031,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="145.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:8" ht="207" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="13" t="s">
         <v>149</v>
       </c>
